--- a/Documents/Arduino_GIGA_R1_pins.xlsx
+++ b/Documents/Arduino_GIGA_R1_pins.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\Arduino_GIGA-stuff\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAA827FC-FD91-4D12-9B84-36C449FA8A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96461F52-168B-40C1-AB92-7A7433C205D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13470" yWindow="945" windowWidth="17940" windowHeight="19215" activeTab="3" xr2:uid="{4DF9CC89-F33A-471A-BC87-D2414FC11F80}"/>
+    <workbookView xWindow="5925" yWindow="1575" windowWidth="25020" windowHeight="19215" activeTab="3" xr2:uid="{4DF9CC89-F33A-471A-BC87-D2414FC11F80}"/>
   </bookViews>
   <sheets>
     <sheet name="All Pins" sheetId="2" r:id="rId1"/>
